--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487819_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487819_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6513</v>
+        <v>4.1599</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6915</v>
+        <v>7.2403</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9598</v>
+        <v>-3.0803</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4869</v>
+        <v>7.0854</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8614000000000001</v>
+        <v>4.1275</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6255</v>
+        <v>2.9579</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2383</v>
+        <v>8.392099999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1189</v>
+        <v>5.724</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1194</v>
+        <v>2.668</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7514</v>
+        <v>-1.3067</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2575</v>
+        <v>-1.5965</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4939</v>
+        <v>0.2898</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2487</v>
+        <v>-3.3299</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7055</v>
+        <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0614</v>
+        <v>0.4418</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1743</v>
+        <v>0.4268</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2356</v>
+        <v>0.0151</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3538</v>
+        <v>-1.9105</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1238</v>
+        <v>1.7513</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>-3.6618</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8661</v>
+        <v>3.8222</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2106</v>
+        <v>2.1853</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3446</v>
+        <v>1.6368</v>
       </c>
       <c r="G3" t="n">
-        <v>7.0854</v>
+        <v>2.4869</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1275</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9579</v>
+        <v>1.6255</v>
       </c>
       <c r="J3" t="n">
-        <v>8.392099999999999</v>
+        <v>3.2383</v>
       </c>
       <c r="K3" t="n">
-        <v>5.724</v>
+        <v>1.1189</v>
       </c>
       <c r="L3" t="n">
-        <v>2.668</v>
+        <v>2.1194</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3067</v>
+        <v>-0.7514</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5965</v>
+        <v>-0.2575</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2898</v>
+        <v>-0.4939</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.4568</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>2.7055</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.852</v>
+        <v>0.2323</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6029</v>
+        <v>0.3196</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2492</v>
+        <v>-0.0873</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.9105</v>
+        <v>-0.3538</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7513</v>
+        <v>-0.1238</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.6618</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9109</v>
+        <v>1.5269</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4614</v>
+        <v>1.3123</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4495</v>
+        <v>0.2146</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9484</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2349</v>
+        <v>-0.1491</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0867</v>
+        <v>-0.0624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1482</v>
+        <v>-0.0867</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>S. CHABI YO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7603</v>
+        <v>0.9972</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6985</v>
+        <v>2.2095</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0618</v>
+        <v>-1.2123</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3268</v>
+        <v>0.5976</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7341</v>
+        <v>-1.0875</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5927</v>
+        <v>1.6851</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0284</v>
+        <v>2.5899</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5684</v>
+        <v>0.8355</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5968</v>
+        <v>1.7545</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2984</v>
+        <v>-1.9924</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3025</v>
+        <v>-1.923</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0041</v>
+        <v>-0.0694</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5564</v>
+        <v>1.0583</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7238</v>
+        <v>1.014</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8326</v>
+        <v>0.0444</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6368</v>
+        <v>-0.8668</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7076</v>
+        <v>-0.3538</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0708</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CHABI YO</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1654</v>
+        <v>0.8497</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4657</v>
+        <v>0.5985</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3003</v>
+        <v>0.2511</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5976</v>
+        <v>-0.6219</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0875</v>
+        <v>-0.4284</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6851</v>
+        <v>-0.1935</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5899</v>
+        <v>-0.1604</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8355</v>
+        <v>-0.6037</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7545</v>
+        <v>0.4433</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9924</v>
+        <v>-0.4615</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.923</v>
+        <v>0.1753</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0694</v>
+        <v>-0.6368</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2265</v>
+        <v>-0.799</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2702</v>
+        <v>-0.4305</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0437</v>
+        <v>-0.3685</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8668</v>
+        <v>0.8137</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3538</v>
+        <v>1.3975</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.513</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0431</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0025</v>
+        <v>2.0716</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0456</v>
+        <v>-2.6124</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6219</v>
+        <v>-1.0856</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4284</v>
+        <v>-0.7696</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1935</v>
+        <v>-0.316</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1604</v>
+        <v>1.5477</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6037</v>
+        <v>0.7247</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4433</v>
+        <v>0.823</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4615</v>
+        <v>-2.6332</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1753</v>
+        <v>-1.4943</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6368</v>
+        <v>-1.1389</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6056</v>
+        <v>1.2867</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0315</v>
+        <v>1.0016</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5741000000000001</v>
+        <v>0.2851</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8137</v>
+        <v>-1.5744</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3975</v>
+        <v>-0.4776</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5838</v>
+        <v>-1.0968</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.86</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8992</v>
+        <v>-1.4865</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7592</v>
+        <v>0.5627</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0856</v>
+        <v>-1.3268</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7696</v>
+        <v>-0.7341</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.316</v>
+        <v>-0.5927</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5477</v>
+        <v>-0.0284</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7247</v>
+        <v>0.5684</v>
       </c>
       <c r="L8" t="n">
-        <v>0.823</v>
+        <v>-0.5968</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6332</v>
+        <v>-1.2984</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4943</v>
+        <v>-1.3025</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1389</v>
+        <v>0.0041</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8325</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9675</v>
+        <v>1.8722</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8292</v>
+        <v>1.5388</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1383</v>
+        <v>0.3334</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5744</v>
+        <v>-0.6368</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4776</v>
+        <v>-0.7076</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0968</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.541</v>
+        <v>-1.4959</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9982</v>
+        <v>-1.0904</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4572</v>
+        <v>-0.4055</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0647</v>
+        <v>-0.912</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2558</v>
+        <v>0.0726</v>
       </c>
       <c r="I9" t="n">
-        <v>0.191</v>
+        <v>-0.9846</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.889</v>
+        <v>-0.8507</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0066</v>
+        <v>-0.2539</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1176</v>
+        <v>-0.5968</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1757</v>
+        <v>-0.0613</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2492</v>
+        <v>0.3265</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0735</v>
+        <v>-0.3878</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8925</v>
+        <v>-0.5839</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.824</v>
+        <v>-0.4253</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9897</v>
+        <v>-1.533</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5843</v>
+        <v>-2.2544</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4055</v>
+        <v>0.7214</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.912</v>
+        <v>-1.0647</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0726</v>
+        <v>-1.2558</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9846</v>
+        <v>0.191</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8507</v>
+        <v>-0.889</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2539</v>
+        <v>-1.0066</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5968</v>
+        <v>0.1176</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0613</v>
+        <v>-0.1757</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3265</v>
+        <v>-0.2492</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3878</v>
+        <v>0.0735</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0778</v>
+        <v>-0.8845</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6524</v>
+        <v>-0.3248</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4253</v>
+        <v>-0.5597</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8247</v>
+        <v>-4.0284</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0616</v>
+        <v>-0.3534</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7631</v>
+        <v>-3.675</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9042</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8018</v>
+        <v>-0.0056</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7581</v>
+        <v>-0.05</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0437</v>
+        <v>0.0444</v>
       </c>
       <c r="V11" t="n">
         <v>-0.743</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.181700000000002</v>
+        <v>2.833899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.7803</v>
+        <v>10.4328</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.598800000000001</v>
+        <v>-7.5989</v>
       </c>
       <c r="G12" t="n">
         <v>0.3063000000000007</v>
@@ -1369,7 +1369,7 @@
         <v>7.799600000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.776</v>
+        <v>4.776000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-12.2693</v>
@@ -1378,7 +1378,7 @@
         <v>-8.7384</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.531000000000001</v>
+        <v>-3.531</v>
       </c>
       <c r="P12" t="n">
         <v>4.162299999999999</v>
@@ -1390,13 +1390,13 @@
         <v>14.5682</v>
       </c>
       <c r="S12" t="n">
-        <v>1.817</v>
+        <v>2.4692</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6222</v>
+        <v>3.2745</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8053</v>
+        <v>-0.8050999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-4.1041</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8824</v>
+        <v>6.995</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9797</v>
+        <v>6.194</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0974</v>
+        <v>0.801</v>
       </c>
       <c r="G13" t="n">
         <v>4.5762</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4451</v>
+        <v>-0.3324</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3171</v>
+        <v>-0.1028</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.128</v>
+        <v>-0.2296</v>
       </c>
       <c r="V13" t="n">
         <v>2.3351</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5898</v>
+        <v>4.1138</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8885</v>
+        <v>2.4243</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7013</v>
+        <v>1.6895</v>
       </c>
       <c r="G14" t="n">
         <v>1.8777</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3275</v>
+        <v>0.1966</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.631</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3035</v>
+        <v>0.2917</v>
       </c>
       <c r="V14" t="n">
         <v>1.4152</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2498</v>
+        <v>2.1084</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1561</v>
+        <v>2.9294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9147</v>
+        <v>2.1114</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2968</v>
+        <v>1.8167</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3821</v>
+        <v>0.2947</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4205</v>
+        <v>3.1485</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9903</v>
+        <v>3.0701</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4108</v>
+        <v>0.0784</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3352</v>
+        <v>-1.0371</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3065</v>
+        <v>-1.2535</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0287</v>
+        <v>0.2164</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4558</v>
+        <v>-0.4807</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7731</v>
+        <v>-0.2191</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6827</v>
+        <v>-0.2616</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1238</v>
+        <v>0.4776</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2112</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3351</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4258</v>
+        <v>1.2935</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8223</v>
+        <v>2.0846</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3965</v>
+        <v>-0.791</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1114</v>
+        <v>-0.9147</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8167</v>
+        <v>-1.2968</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2947</v>
+        <v>0.3821</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1485</v>
+        <v>0.4205</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0701</v>
+        <v>-0.9903</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0784</v>
+        <v>1.4108</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0371</v>
+        <v>-1.3352</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2535</v>
+        <v>-0.3065</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2164</v>
+        <v>-1.0287</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1632</v>
+        <v>1.4996</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3262</v>
+        <v>0.7016</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.837</v>
+        <v>0.798</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4776</v>
+        <v>-0.1238</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.2112</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4776</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2661</v>
+        <v>-0.0196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8255</v>
+        <v>0.3969</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5594</v>
+        <v>-0.4165</v>
       </c>
       <c r="G17" t="n">
         <v>0.0086</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5063</v>
+        <v>0.2205</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6491</v>
+        <v>0.2205</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1429</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0.5838</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. ALVAREZ FERNANDEZ</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9659</v>
+        <v>-0.7548</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6075</v>
+        <v>0.1386</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3584</v>
+        <v>-0.8934</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7918</v>
+        <v>-0.1976</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4112</v>
+        <v>-0.147</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3806</v>
+        <v>-0.0506</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1385</v>
+        <v>1.1784</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1727</v>
+        <v>0.7351</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3112</v>
+        <v>0.4433</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6533</v>
+        <v>-1.3761</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5839</v>
+        <v>-0.8821</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0694</v>
+        <v>-0.4939</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2016</v>
+        <v>-0.7028</v>
       </c>
       <c r="T18" t="n">
-        <v>0.531</v>
+        <v>-0.1261</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3294</v>
+        <v>-0.5767</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>I. ALVAREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8278</v>
+        <v>-1.0564</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1829</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.645</v>
+        <v>-0.1275</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1976</v>
+        <v>-1.7918</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.147</v>
+        <v>-0.4112</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0506</v>
+        <v>-1.3806</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1784</v>
+        <v>-1.1385</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7351</v>
+        <v>0.1727</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4433</v>
+        <v>-1.3112</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3761</v>
+        <v>-0.6533</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8821</v>
+        <v>-0.5839</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4939</v>
+        <v>-0.0694</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7759</v>
+        <v>0.1111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4476</v>
+        <v>0.2096</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3282</v>
+        <v>-0.0985</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.396</v>
+        <v>-3.1416</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0785</v>
+        <v>-2.9609</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3175</v>
+        <v>-0.1807</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9329</v>
+        <v>-0.8981</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6143</v>
+        <v>-0.2622</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3186</v>
+        <v>-0.636</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0346</v>
+        <v>0.1471</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3941</v>
+        <v>0.3218</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4287</v>
+        <v>-0.1747</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8983</v>
+        <v>-1.0452</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0084</v>
+        <v>-0.5839</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8899</v>
+        <v>-0.4613</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8325</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2487</v>
+        <v>-3.3299</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.8783</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0373</v>
+        <v>0.222</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0842</v>
+        <v>0.6564</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6735</v>
+        <v>-3.808</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4967</v>
+        <v>-0.7214</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1768</v>
+        <v>-3.0866</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8981</v>
+        <v>-2.9329</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2622</v>
+        <v>-0.6143</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.636</v>
+        <v>-2.3186</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1471</v>
+        <v>-1.0346</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3218</v>
+        <v>0.3941</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1747</v>
+        <v>-1.4287</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0452</v>
+        <v>-1.8983</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5839</v>
+        <v>-1.0084</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4613</v>
+        <v>-0.8899</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1218</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3464</v>
+        <v>0.5411</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3138</v>
+        <v>0.3944</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6603</v>
+        <v>0.1468</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7322</v>
+        <v>-5.0544</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7078</v>
+        <v>-1.9577</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.0244</v>
+        <v>-3.0966</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1449</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.5685</v>
+        <v>-0.8907</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1496</v>
+        <v>-0.3995</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4189</v>
+        <v>-0.4912</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3538</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.181500000000001</v>
+        <v>0.6758999999999995</v>
       </c>
       <c r="E23" t="n">
-        <v>7.598699999999997</v>
+        <v>7.5989</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.7804</v>
+        <v>-6.9229</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3060999999999994</v>
+        <v>-0.3060999999999989</v>
       </c>
       <c r="H23" t="n">
         <v>0.9388000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.245000000000001</v>
+        <v>-1.245</v>
       </c>
       <c r="J23" t="n">
         <v>12.2693</v>
@@ -2227,7 +2227,7 @@
         <v>8.738300000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>3.531100000000001</v>
+        <v>3.5311</v>
       </c>
       <c r="M23" t="n">
         <v>-12.5757</v>
@@ -2248,13 +2248,13 @@
         <v>10.4059</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.817</v>
+        <v>1.0406</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8052000000000001</v>
+        <v>0.8053999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6221</v>
+        <v>0.2353</v>
       </c>
       <c r="V23" t="n">
         <v>4.1041</v>
